--- a/output/laminas_comunales/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/laminas_comunales/comunal_p_basica_a_2020_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C442"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,121 +375,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C2">
-        <v>48.61495971679688</v>
+        <v>129941.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C3">
-        <v>45.16711807250977</v>
+        <v>126951.921875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C4">
-        <v>43.22638320922852</v>
+        <v>126374.40625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C5">
-        <v>39.49580001831055</v>
+        <v>124383.390625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="C6">
-        <v>37.14821624755859</v>
+        <v>124129.1875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C7">
-        <v>35.42688751220703</v>
+        <v>123884.6796875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C8">
-        <v>34.77406692504883</v>
+        <v>123635.1484375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="C9">
-        <v>34.06901931762695</v>
+        <v>123408.546875</v>
       </c>
     </row>
     <row r="10">
@@ -504,127 +504,127 @@
         </is>
       </c>
       <c r="C10">
-        <v>31.71091461181641</v>
+        <v>123135.3984375</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="C11">
-        <v>30.83773994445801</v>
+        <v>122604.1796875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C12">
-        <v>30.29144859313965</v>
+        <v>121774.546875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ranquil</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C13">
-        <v>30.15625</v>
+        <v>121648.5703125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C14">
-        <v>30.10872650146484</v>
+        <v>121490.3984375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C15">
-        <v>29.79684066772461</v>
+        <v>121247.078125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C16">
-        <v>29.42817306518555</v>
+        <v>120990.359375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="C17">
-        <v>27.5296573638916</v>
+        <v>120630.1875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C18">
-        <v>26.79959487915039</v>
+        <v>120522.5703125</v>
       </c>
     </row>
     <row r="19">
@@ -639,52 +639,6352 @@
         </is>
       </c>
       <c r="C19">
-        <v>25.47748565673828</v>
+        <v>120082.0625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C20">
-        <v>23.90817451477051</v>
+        <v>119911.65625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C21">
-        <v>23.22922515869141</v>
+        <v>119625.2421875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>118597.859375</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>118527.0703125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>118522.2578125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>118305.390625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>118156.0078125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>117999.5546875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>117502.9375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>117393.6953125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>117363.8984375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>117256.2109375</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>117233.75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>117005.171875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>116634.6171875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>116306.234375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>116302.7109375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>116241.109375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>116150.71875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>116143.4296875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>116125.78125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>116103.84375</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>115648.6484375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>115603.1171875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>115544.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>115481.640625</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>115439.640625</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>115422.6640625</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>115368.6875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>115365.4609375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>114967.8125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>114964.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>114884.390625</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>114864.9453125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>114864.734375</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>114859.265625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>114827.171875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>114662.296875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>16101</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Chillán</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C58">
+        <v>114547.1640625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>114501.25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>114480.71875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>114259.9921875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>114239.609375</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>114212.4453125</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>114176.9609375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>114148.6796875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>114078.21875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>114003.6171875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>113954.671875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>113949.8984375</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>113902.5703125</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>113847.8515625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>113711.96875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>113554.6796875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>113521.3359375</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>113488.7421875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>113317.984375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>113239.8828125</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>113235.1015625</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>113173.171875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>113147.2578125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>113102.703125</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>113074.6640625</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>113023.6953125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>112778.203125</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>112660.4609375</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>112627.1640625</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>112448.9765625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>112305.6640625</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>112282.0625</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>112162.0859375</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>111842.7734375</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>111775.7734375</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>111608.875</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>111552.9765625</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>111444.078125</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>111395.7265625</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>111313.3515625</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>111196.640625</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>110982.3515625</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>110818.1796875</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>110590.9375</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>110547.90625</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>110410.5234375</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>110234.109375</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>109841.0546875</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>109798.734375</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>109698.2734375</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>109690.375</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>109452.5859375</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>109256.125</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>109093.234375</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>109056.34375</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>108912.5546875</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>108806.84375</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>108307.2578125</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>108174.484375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>108108.6484375</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>108032.015625</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>107954.2734375</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>107909.1875</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>107575.3828125</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>107495.203125</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>107196.2265625</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>107177.34375</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>106954.1640625</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>106441.828125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>105900.9140625</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>105355.515625</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>105176.6796875</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>104801.453125</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>104757.59375</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>104714.2890625</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>103478.03125</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>103385.59375</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>103288.9140625</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>102876.21875</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>102714.6640625</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>102287.2265625</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>102277.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>102044.6328125</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>101416.890625</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>101413.2578125</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>101310.5546875</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>101015.171875</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>100346.59375</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>99093.46875</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>99085.2265625</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>97878.4375</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>61.18754577636719</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>61.09889984130859</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>59.93265914916992</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>59.59302139282227</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>57.08661270141602</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>55.87863540649414</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>55.62200927734375</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>55.61497497558594</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>55.59321975708008</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>55.51601409912109</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>55.49348068237305</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>55.29905700683594</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>54.82573699951172</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>54.74822616577148</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>54.71039962768555</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>54.48275756835938</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>54.44527816772461</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>54.25170135498047</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>53.68852615356445</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>53.66169738769531</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>53.515625</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>52.90237426757813</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>52.70935821533203</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>52.56124877929688</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>52.2768669128418</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>52.18658828735352</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>52.12121200561523</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>52.08877182006836</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>51.78282165527344</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>51.68646240234375</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>51.43513107299805</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>51.28276443481445</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>51.17116928100586</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>51.0638313293457</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>50.92024612426758</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>50.85324096679688</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>50.75493621826172</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>50.66079330444336</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>50.33783721923828</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>50.22644805908203</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>50.11219024658203</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>49.9283332824707</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>49.78947448730469</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>49.71098327636719</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>49.52740859985352</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>49.50859832763672</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>49.48604965209961</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>49.47368240356445</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>49.4522705078125</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>49.42965698242188</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>49.4195671081543</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>49.36708831787109</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>49.34333801269531</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>49.27536392211914</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>49.16013336181641</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>49.12461471557617</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>49.11280059814453</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>48.93917846679688</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>48.90382385253906</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>48.90073394775391</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>48.85844802856445</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>48.84910583496094</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>48.82175064086914</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>48.79032135009766</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>48.76486587524414</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>48.61495971679688</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>48.61111068725586</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>48.60166168212891</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>48.58412170410156</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>48.56961822509766</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>48.53420257568359</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>48.52652359008789</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>48.47328186035156</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>48.38212585449219</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>48.20359420776367</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>48.06568145751953</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>48.06295394897461</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>47.95918273925781</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>47.91878509521484</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>47.91044616699219</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>47.89065933227539</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>47.85714340209961</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>47.83118438720703</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>47.62979507446289</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>47.57281494140625</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>47.47504425048828</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>47.45500183105469</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>47.4040641784668</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>47.17832946777344</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>46.97023010253906</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>46.94533920288086</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>46.53649520874023</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>46.36627960205078</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>46.27450942993164</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>46.26334381103516</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>46.25850296020508</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>46.04072570800781</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>45.99156188964844</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>45.83217239379883</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>45.81280899047852</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>45.53440856933594</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>45.47085189819336</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>45.43859481811523</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>45.39715957641602</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>45.35792922973633</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>45.35714340209961</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>45.35519027709961</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>45.30988311767578</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>45.18388748168945</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>45.16711807250977</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>45.14446258544922</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>45.12428283691406</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>44.98525238037109</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>44.82758712768555</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>44.72049713134766</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>44.64742279052734</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>44.61105728149414</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>44.60641479492188</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>44.21001052856445</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>43.97163009643555</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>43.96551895141602</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>43.89857482910156</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>43.81884765625</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>43.77990341186523</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>43.77104187011719</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>43.76705932617188</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>43.66729736328125</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>43.4034423828125</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>43.22638320922852</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>43.22111129760742</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>43.10953903198242</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>43.10018920898438</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>43.05710983276367</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>43.04347991943359</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>42.96875</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>42.92845153808594</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>42.68292617797852</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>42.62295150756836</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>42.52525329589844</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>42.47226715087891</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>42.44741821289063</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>42.32424545288086</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>42.18181991577148</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>42.17391204833984</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>42.12828063964844</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>41.91919326782227</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>41.62479019165039</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>41.44385147094727</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>41.30018997192383</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>41.08108139038086</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>40.94766616821289</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>40.8805046081543</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>40.87345886230469</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>40.81632614135742</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>40.74074172973633</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>40.64386367797852</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>40.452392578125</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>40.43583679199219</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>40.39408874511719</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>40.15625</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>39.79591751098633</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>39.73758316040039</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>39.49580001831055</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>39.42751693725586</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>39.23611068725586</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>39.03420639038086</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>38.91891860961914</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>38.79003524780273</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>38.70752716064453</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>38.51852035522461</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>38.42105102539063</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>38.40579605102539</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>38.33967208862305</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>37.94038009643555</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>37.85714340209961</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>37.69751739501953</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>37.58865356445313</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>37.54448318481445</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>37.25490188598633</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>37.19512176513672</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>37.14821624755859</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>37.02289962768555</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>36.95652008056641</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>36.81972885131836</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>36.7088623046875</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>36.69355010986328</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>36.15494918823242</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>36.06557464599609</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>36.04240417480469</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>35.77586364746094</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>35.53459167480469</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>35.42688751220703</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>35.29411697387695</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>35.02994155883789</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>34.97536849975586</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>34.77406692504883</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>34.06901931762695</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>33.94317626953125</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>33.92070388793945</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>33.4782600402832</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>33.45935821533203</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>33.27495574951172</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>32.99232864379883</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>32.97297286987305</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>32.75862121582031</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>32.72727203369141</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>32.65518951416016</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>32.37704849243164</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>32.20338821411133</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>31.81818199157715</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>31.74061393737793</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>31.71091461181641</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>31.69398880004883</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>31.13068962097168</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>31.11480903625488</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>30.96695137023926</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>30.89285659790039</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>30.83773994445801</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>30.52631568908691</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>30.43478202819824</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>30.32069969177246</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>30.29144859313965</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>30.29126167297363</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>30.15625</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>30.10872650146484</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>29.79684066772461</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>29.7297306060791</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>29.68337821960449</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>29.42817306518555</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>29.42583656311035</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>29.40287208557129</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>29.30832290649414</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>28.99515724182129</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>28.96174812316895</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>28.9017333984375</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>28.55603408813477</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>28.19767379760742</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>28.0623607635498</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>27.8538818359375</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>27.5296573638916</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>27.39557647705078</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>27.37920951843262</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>27.18078422546387</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>27.17291831970215</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>26.91729354858398</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>26.79959487915039</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>26.77966117858887</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>26.40642929077148</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>26.00536155700684</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>25.90011596679688</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>25.84670257568359</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>25.70480918884277</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>25.65656471252441</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>25.47748565673828</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>25.33470726013184</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>24.99193572998047</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>24.95471000671387</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>24.95344543457031</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>24.65166091918945</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>24.64712333679199</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>24.18052291870117</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>24.05063247680664</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>23.90817451477051</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>23.72881317138672</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>23.54651069641113</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>23.44801712036133</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>23.22922515869141</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>22.86995506286621</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>21.89616203308105</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>21.54047012329102</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>21.47583770751953</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>20.56663131713867</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>20.03546142578125</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>19.93517112731934</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>19.43364715576172</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>18.89952087402344</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>18.77100372314453</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C430">
         <v>18.65747451782227</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>18.5074634552002</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>18.33529090881348</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>17.84511756896973</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>16.92913436889648</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>16.16660690307617</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>15.62734794616699</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>15.2380952835083</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>15.01901149749756</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>13.77643489837646</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>13.61332321166992</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>12.76733589172363</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>9.768241882324219</v>
       </c>
     </row>
   </sheetData>
